--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FeverApps\123\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFAEA01-F43A-4DA7-9346-4721B542FB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8F9DAA-2B2C-4004-AD84-40831F9A9D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2095" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="1526">
   <si>
     <t>英雄编号</t>
   </si>
@@ -1552,6 +1552,9 @@
     <t>2025-08-04 18:47:32</t>
   </si>
   <si>
+    <t>王维</t>
+  </si>
+  <si>
     <t>2026-08-20 10:57:04</t>
   </si>
   <si>
@@ -4069,6 +4072,9 @@
     <t>2023-06-19 16:31:45</t>
   </si>
   <si>
+    <t>2026-08-26 15:03:39</t>
+  </si>
+  <si>
     <t>蒙恬</t>
   </si>
   <si>
@@ -4594,11 +4600,7 @@
     <t>刀锋宝贝</t>
   </si>
   <si>
-    <t>王维</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>原皮</t>
+    <t>傩神司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4628,7 +4630,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4642,13 +4644,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -4664,7 +4671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4672,10 +4679,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5029,130 +5039,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -12675,13 +12685,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>1524</v>
-      </c>
-      <c r="D139" s="4" t="s">
         <v>509</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -12727,40 +12737,40 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>452</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>116</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L140" s="2" t="s">
         <v>219</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N140" s="2" t="s">
         <v>354</v>
@@ -12769,13 +12779,13 @@
         <v>338</v>
       </c>
       <c r="P140" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Q140" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="R140" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
@@ -12807,63 +12817,63 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
       <c r="M141" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P141" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Q141" s="2" t="s">
         <v>338</v>
       </c>
       <c r="R141" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T141" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="U141" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="V141" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
@@ -12891,69 +12901,69 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>354</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
       <c r="O142" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q142" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="R142" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="T142" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="U142" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="V142" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="W142" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="X142" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Y142" s="2" t="s">
         <v>321</v>
@@ -12962,16 +12972,16 @@
         <v>322</v>
       </c>
       <c r="AA142" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AB142" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AC142" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AD142" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AE142" s="1"/>
       <c r="AF142" s="1"/>
@@ -12991,75 +13001,75 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M143" s="2" t="s">
         <v>127</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P143" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Q143" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="R143" s="2" t="s">
         <v>162</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="T143" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="U143" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="V143" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
       <c r="Y143" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z143" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
@@ -13129,16 +13139,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>166</v>
@@ -13150,46 +13160,46 @@
         <v>354</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>435</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>452</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P145" s="2" t="s">
         <v>100</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="S145" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="T145" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="U145" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="V145" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
@@ -13263,63 +13273,63 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E147" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="L147" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="L147" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="M147" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P147" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="R147" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
       <c r="U147" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
@@ -13393,51 +13403,51 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G149" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="H149" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="I149" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
       <c r="O149" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P149" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="R149" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -13469,45 +13479,45 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
       <c r="I150" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>122</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
@@ -13541,69 +13551,69 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>166</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P151" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Q151" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="T151" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="X151" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
@@ -13629,27 +13639,27 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
       <c r="I152" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
@@ -13689,79 +13699,79 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
       <c r="O153" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P153" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="T153" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="U153" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="W153" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="X153" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
       <c r="AC153" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AD153" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AE153" s="1"/>
       <c r="AF153" s="1"/>
@@ -13781,7 +13791,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>43</v>
@@ -13790,58 +13800,58 @@
         <v>152</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I154" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="J154" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="J154" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="K154" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P154" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="T154" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="U154" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
@@ -13869,73 +13879,73 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L155" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="Q155" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="R155" s="2" t="s">
         <v>452</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="T155" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="U155" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="W155" s="2" t="s">
         <v>157</v>
       </c>
       <c r="X155" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
@@ -13961,55 +13971,55 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P156" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
@@ -14041,67 +14051,67 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="P157" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="R157" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="T157" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="U157" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
@@ -14129,7 +14139,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>43</v>
@@ -14138,22 +14148,22 @@
         <v>354</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
@@ -14239,43 +14249,43 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
@@ -14403,25 +14413,25 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -14463,7 +14473,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>43</v>
@@ -14472,16 +14482,16 @@
         <v>76</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -14615,67 +14625,67 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>116</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="R167" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="T167" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="U167" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="V167" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
@@ -14703,73 +14713,73 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="O168" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="Q168" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="R168" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="T168" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="U168" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="V168" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="W168" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="X168" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="Y168" s="2" t="s">
         <v>104</v>
@@ -14799,7 +14809,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>43</v>
@@ -14808,46 +14818,46 @@
         <v>146</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>452</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="O169" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P169" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="R169" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -14879,85 +14889,85 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O170" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Q170" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="R170" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="T170" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="U170" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="V170" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="W170" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="X170" s="2" t="s">
         <v>419</v>
       </c>
       <c r="Y170" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="Z170" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AA170" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AB170" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
@@ -14979,7 +14989,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>43</v>
@@ -14988,56 +14998,56 @@
         <v>500</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G171" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="J171" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="H171" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="I171" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="J171" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="K171" s="2" t="s">
         <v>155</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O171" s="2" t="s">
         <v>338</v>
       </c>
       <c r="P171" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="T171" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="X171" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
@@ -15063,7 +15073,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>43</v>
@@ -15072,44 +15082,44 @@
         <v>500</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
       <c r="K172" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M172" s="2" t="s">
         <v>338</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="T172" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
@@ -15139,19 +15149,19 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
@@ -15195,61 +15205,61 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="O174" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="Q174" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="R174" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="T174" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="U174" s="2" t="s">
         <v>176</v>
@@ -15260,10 +15270,10 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Z174" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
@@ -15287,7 +15297,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>43</v>
@@ -15296,34 +15306,34 @@
         <v>100</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>488</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>500</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>100</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
@@ -15334,28 +15344,28 @@
         <v>491</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="T175" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="U175" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="V175" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="W175" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="X175" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="Y175" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="Z175" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
@@ -15379,19 +15389,19 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>104</v>
@@ -15400,28 +15410,28 @@
         <v>100</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O176" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
@@ -15455,22 +15465,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>456</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>100</v>
@@ -15478,22 +15488,22 @@
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
       <c r="K177" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="O177" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="P177" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
@@ -15527,33 +15537,33 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
       <c r="I178" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
@@ -15591,40 +15601,40 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G179" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="H179" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="H179" s="2" t="s">
-        <v>891</v>
-      </c>
       <c r="I179" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>274</v>
@@ -15632,22 +15642,22 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="Q179" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="T179" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="U179" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
@@ -15675,43 +15685,43 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
@@ -15747,7 +15757,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>43</v>
@@ -15756,46 +15766,46 @@
         <v>76</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -15873,61 +15883,61 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="R183" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="S183" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="T183" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
@@ -15957,55 +15967,55 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G184" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="H184" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="H184" s="2" t="s">
-        <v>941</v>
-      </c>
       <c r="I184" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
@@ -16037,77 +16047,77 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>500</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="L185" s="2" t="s">
         <v>76</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="P185" s="2" t="s">
         <v>209</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="T185" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="X185" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
       <c r="AA185" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AB185" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
@@ -16175,51 +16185,51 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>116</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
       <c r="O187" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="P187" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
@@ -16251,43 +16261,43 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
@@ -16323,19 +16333,19 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
@@ -16379,57 +16389,57 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>456</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="T190" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
@@ -16459,63 +16469,63 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="O191" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="P191" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="Q191" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="R191" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
       <c r="U191" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="V191" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
@@ -16543,7 +16553,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>43</v>
@@ -16552,46 +16562,46 @@
         <v>122</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O192" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="Q192" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="S192" s="2" t="s">
         <v>127</v>
@@ -16600,16 +16610,16 @@
         <v>175</v>
       </c>
       <c r="U192" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="V192" s="2" t="s">
         <v>162</v>
       </c>
       <c r="W192" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="X192" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
@@ -16635,41 +16645,41 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
       <c r="I193" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
       <c r="O193" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="P193" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
@@ -16677,7 +16687,7 @@
         <v>338</v>
       </c>
       <c r="T193" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -16707,67 +16717,67 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L194" s="2" t="s">
         <v>205</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="Q194" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="T194" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="U194" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="V194" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
@@ -16795,7 +16805,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>43</v>
@@ -16804,40 +16814,40 @@
         <v>219</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="P195" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
@@ -16871,49 +16881,49 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="L196" s="2" t="s">
         <v>219</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="O196" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
@@ -16947,16 +16957,16 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>100</v>
@@ -16964,45 +16974,45 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
       <c r="I197" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O197" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="P197" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="Q197" s="2" t="s">
         <v>338</v>
       </c>
       <c r="R197" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
       <c r="U197" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="V197" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="W197" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="X197" s="2" t="s">
         <v>276</v>
@@ -17031,49 +17041,49 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="O198" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
@@ -17107,43 +17117,43 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -17179,69 +17189,69 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>354</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="O200" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
       <c r="U200" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="V200" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="W200" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="X200" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
@@ -22419,61 +22429,61 @@
         <v>312</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="J313" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="K313" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="L313" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="M313" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N313" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="O313" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="P313" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="Q313" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="R313" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="S313" s="2" t="s">
         <v>210</v>
       </c>
       <c r="T313" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
@@ -31151,7 +31161,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>43</v>
@@ -31160,52 +31170,52 @@
         <v>354</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F502" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="K502" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="L502" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="M502" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="N502" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="P502" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="Q502" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="R502" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="T502" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="U502" s="1"/>
       <c r="V502" s="1"/>
@@ -31235,57 +31245,57 @@
         <v>502</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>124</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I503" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J503" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="J503" s="2" t="s">
-        <v>1152</v>
-      </c>
       <c r="K503" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="L503" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="M503" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N503" s="2" t="s">
         <v>50</v>
       </c>
       <c r="O503" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="P503" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="Q503" s="1"/>
       <c r="R503" s="1"/>
       <c r="S503" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="T503" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="U503" s="1"/>
       <c r="V503" s="1"/>
@@ -31315,47 +31325,47 @@
         <v>503</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K504" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="L504" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="M504" s="1"/>
       <c r="N504" s="1"/>
       <c r="O504" s="1"/>
       <c r="P504" s="1"/>
       <c r="Q504" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="R504" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="S504" s="1"/>
       <c r="T504" s="1"/>
@@ -31387,55 +31397,55 @@
         <v>504</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H505" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I505" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="K505" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="L505" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="M505" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N505" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="O505" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="P505" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q505" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="R505" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="S505" s="1"/>
       <c r="T505" s="1"/>
@@ -31467,55 +31477,55 @@
         <v>505</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I506" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="K506" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="L506" s="2" t="s">
         <v>68</v>
       </c>
       <c r="M506" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N506" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="O506" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="P506" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="Q506" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="R506" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S506" s="1"/>
       <c r="T506" s="1"/>
@@ -31547,43 +31557,43 @@
         <v>506</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I507" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="K507" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L507" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M507" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="N507" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="O507" s="1"/>
       <c r="P507" s="1"/>
@@ -31619,37 +31629,37 @@
         <v>507</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F508" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G508" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H508" s="2" t="s">
         <v>452</v>
       </c>
       <c r="I508" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="J508" s="2" t="s">
         <v>68</v>
       </c>
       <c r="K508" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="L508" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>
@@ -31687,63 +31697,63 @@
         <v>508</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="F509" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G509" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="I509" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="J509" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="J509" s="2" t="s">
-        <v>1210</v>
-      </c>
       <c r="K509" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="L509" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M509" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N509" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="P509" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="Q509" s="1"/>
       <c r="R509" s="1"/>
       <c r="S509" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="T509" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="U509" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="V509" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="W509" s="1"/>
       <c r="X509" s="1"/>
@@ -31771,37 +31781,37 @@
         <v>509</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F510" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G510" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="I510" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J510" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K510" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="L510" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="M510" s="1"/>
       <c r="N510" s="1"/>
@@ -31839,7 +31849,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>43</v>
@@ -31848,37 +31858,37 @@
         <v>452</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F511" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G511" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="I511" s="2" t="s">
         <v>153</v>
       </c>
       <c r="J511" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="K511" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="L511" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="M511" s="2" t="s">
         <v>127</v>
       </c>
       <c r="N511" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="P511" s="2" t="s">
         <v>162</v>
@@ -31919,45 +31929,45 @@
         <v>511</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F512" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="K512" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="L512" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M512" s="1"/>
       <c r="N512" s="1"/>
       <c r="O512" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="P512" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="Q512" s="1"/>
       <c r="R512" s="1"/>
@@ -32037,57 +32047,57 @@
         <v>513</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="K514" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="L514" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="M514" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N514" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="O514" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P514" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Q514" s="1"/>
       <c r="R514" s="1"/>
       <c r="S514" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="T514" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="U514" s="1"/>
       <c r="V514" s="1"/>
@@ -32117,37 +32127,37 @@
         <v>514</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="I515" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="K515" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="L515" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="M515" s="1"/>
       <c r="N515" s="1"/>
@@ -32185,49 +32195,49 @@
         <v>515</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F516" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="I516" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="J516" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="K516" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="L516" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="M516" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N516" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="O516" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="P516" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="Q516" s="1"/>
       <c r="R516" s="1"/>
@@ -32307,37 +32317,37 @@
         <v>517</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F518" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G518" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="I518" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="J518" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="K518" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="L518" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="M518" s="1"/>
       <c r="N518" s="1"/>
@@ -32375,7 +32385,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>43</v>
@@ -32384,42 +32394,42 @@
         <v>500</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="F519" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
       <c r="I519" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="J519" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="K519" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="L519" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="M519" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N519" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="O519" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="P519" s="2" t="s">
         <v>265</v>
       </c>
       <c r="Q519" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="R519" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="S519" s="1"/>
       <c r="T519" s="1"/>
@@ -32451,25 +32461,25 @@
         <v>519</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="F520" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="G520" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -32557,50 +32567,50 @@
         <v>521</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F522" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="K522" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="L522" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="M522" s="1"/>
       <c r="N522" s="1"/>
       <c r="O522" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="P522" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="Q522" s="1"/>
       <c r="R522" s="1"/>
       <c r="S522" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="T522" s="2" t="s">
         <v>276</v>
@@ -32633,13 +32643,13 @@
         <v>522</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>258</v>
@@ -32648,28 +32658,28 @@
         <v>452</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="K523" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="L523" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="M523" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="N523" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="O523" s="1"/>
       <c r="P523" s="1"/>
@@ -32705,13 +32715,13 @@
         <v>523</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>258</v>
@@ -32722,46 +32732,46 @@
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
       <c r="I524" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="K524" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="L524" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="M524" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="N524" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="O524" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="P524" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="Q524" s="2" t="s">
         <v>373</v>
       </c>
       <c r="R524" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="T524" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="U524" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="V524" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="W524" s="1"/>
       <c r="X524" s="1"/>
@@ -32789,7 +32799,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>43</v>
@@ -32801,37 +32811,37 @@
         <v>258</v>
       </c>
       <c r="F525" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H525" s="2" t="s">
         <v>500</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="K525" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="L525" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="M525" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="N525" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="O525" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="P525" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="Q525" s="1"/>
       <c r="R525" s="1"/>
@@ -32865,40 +32875,44 @@
         <v>525</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>258</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H526" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I526" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="K526" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="L526" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="M526" s="1"/>
-      <c r="N526" s="1"/>
+        <v>1348</v>
+      </c>
+      <c r="M526" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="N526" s="5" t="s">
+        <v>1349</v>
+      </c>
       <c r="O526" s="1"/>
       <c r="P526" s="1"/>
       <c r="Q526" s="1"/>
@@ -32979,37 +32993,37 @@
         <v>527</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G528" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="I528" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="J528" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="K528" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="L528" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="M528" s="1"/>
       <c r="N528" s="1"/>
@@ -33047,51 +33061,51 @@
         <v>528</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="G529" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="I529" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="J529" s="2" t="s">
         <v>209</v>
       </c>
       <c r="K529" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="L529" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="M529" s="1"/>
       <c r="N529" s="1"/>
       <c r="O529" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="P529" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="Q529" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="R529" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="S529" s="1"/>
       <c r="T529" s="1"/>
@@ -33123,51 +33137,51 @@
         <v>529</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="F530" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="I530" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="J530" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="K530" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="L530" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="M530" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="N530" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="O530" s="1"/>
       <c r="P530" s="1"/>
       <c r="Q530" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="R530" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="S530" s="1"/>
       <c r="T530" s="1"/>
@@ -33199,25 +33213,25 @@
         <v>530</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>407</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="G531" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="I531" s="1"/>
       <c r="J531" s="1"/>
@@ -33225,25 +33239,25 @@
         <v>410</v>
       </c>
       <c r="L531" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="M531" s="2" t="s">
         <v>412</v>
       </c>
       <c r="N531" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="O531" s="2" t="s">
         <v>414</v>
       </c>
       <c r="P531" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="Q531" s="2" t="s">
         <v>416</v>
       </c>
       <c r="R531" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="S531" s="1"/>
       <c r="T531" s="1"/>
@@ -33275,49 +33289,49 @@
         <v>531</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="F532" s="2" t="s">
         <v>452</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="K532" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="L532" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="M532" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N532" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="O532" s="2" t="s">
         <v>492</v>
       </c>
       <c r="P532" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="Q532" s="1"/>
       <c r="R532" s="1"/>
@@ -33397,37 +33411,37 @@
         <v>533</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F534" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H534" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="I534" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="K534" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="L534" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M534" s="1"/>
       <c r="N534" s="1"/>
@@ -33465,49 +33479,49 @@
         <v>534</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K535" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="L535" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="M535" s="2" t="s">
         <v>71</v>
       </c>
       <c r="N535" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="O535" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="P535" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="Q535" s="1"/>
       <c r="R535" s="1"/>
@@ -33587,25 +33601,25 @@
         <v>536</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="F537" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -33647,31 +33661,31 @@
         <v>537</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="F538" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="G538" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="H538" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I538" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="J538" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="K538" s="1"/>
       <c r="L538" s="1"/>
@@ -33711,43 +33725,43 @@
         <v>538</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F539" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="G539" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="H539" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="I539" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="J539" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="K539" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="L539" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="M539" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="N539" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="O539" s="1"/>
       <c r="P539" s="1"/>
@@ -33829,31 +33843,31 @@
         <v>540</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="G541" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="J541" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K541" s="1"/>
       <c r="L541" s="1"/>
@@ -33939,39 +33953,39 @@
         <v>542</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="F543" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="G543" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="I543" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J543" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K543" s="1"/>
       <c r="L543" s="1"/>
       <c r="M543" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="N543" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="O543" s="1"/>
       <c r="P543" s="1"/>
@@ -34053,39 +34067,39 @@
         <v>544</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="G545" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="I545" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="J545" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="K545" s="1"/>
       <c r="L545" s="1"/>
       <c r="M545" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="N545" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="O545" s="1"/>
       <c r="P545" s="1"/>
@@ -34121,41 +34135,41 @@
         <v>545</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F546" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="G546" s="2" t="s">
         <v>153</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
       <c r="K546" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L546" s="2" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
       <c r="O546" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="P546" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="Q546" s="1"/>
       <c r="R546" s="1"/>
@@ -34235,13 +34249,13 @@
         <v>547</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E548" s="1"/>
       <c r="F548" s="1"/>
@@ -34287,28 +34301,28 @@
         <v>548</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F549" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G549" s="2" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="I549" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="J549" s="2" t="s">
         <v>305</v>
@@ -34351,19 +34365,19 @@
         <v>549</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
@@ -34407,16 +34421,16 @@
         <v>550</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>251</v>
@@ -34785,25 +34799,25 @@
         <v>558</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="F559" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G559" s="2" t="s">
         <v>338</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="I559" s="1"/>
       <c r="J559" s="1"/>
@@ -35029,33 +35043,33 @@
         <v>563</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="G564" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="H564" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
       <c r="K564" s="2" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="L564" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
@@ -35093,53 +35107,53 @@
         <v>564</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="G565" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
       <c r="K565" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="L565" s="2" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="M565" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="N565" s="2" t="s">
         <v>143</v>
       </c>
       <c r="O565" s="2" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="P565" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="Q565" s="1"/>
       <c r="R565" s="1"/>
       <c r="S565" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="T565" s="2" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="U565" s="1"/>
       <c r="V565" s="1"/>
@@ -35721,33 +35735,33 @@
         <v>577</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G578" s="2" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
       <c r="K578" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="M578" s="1"/>
       <c r="N578" s="1"/>
@@ -38223,13 +38237,13 @@
         <v>631</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="E632" s="1"/>
       <c r="F632" s="1"/>
@@ -38413,13 +38427,13 @@
         <v>635</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="E636" s="1"/>
       <c r="F636" s="1"/>
@@ -38649,13 +38663,13 @@
         <v>640</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="E641" s="1"/>
       <c r="F641" s="1"/>
@@ -38931,13 +38945,13 @@
         <v>646</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="E647" s="1"/>
       <c r="F647" s="1"/>
@@ -55217,7 +55231,7 @@
       <c r="AP1000" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP1000" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:AP1000" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="3">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -54909,9 +54909,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP1000">
-    <filterColumn colId="3">
+    <filterColumn colId="3" hiddenButton="0" showButton="1">
       <customFilters>
-        <customFilter operator="notEqual" val=" "/>
+        <customFilter val=" " operator="notEqual"/>
       </customFilters>
     </filterColumn>
   </autoFilter>

--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -100,13 +105,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,212 +530,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>英雄编号</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>英雄名字</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>00-皮肤名</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>00-Last-Modified</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>01-皮肤名</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>01-Last-Modified</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>02-皮肤名</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>02-Last-Modified</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>03-皮肤名</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>03-Last-Modified</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>04-皮肤名</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>04-Last-Modified</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>05-皮肤名</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>05-Last-Modified</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>06-皮肤名</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>06-Last-Modified</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>07-皮肤名</t>
         </is>
       </c>
-      <c r="R1" s="6" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>07-Last-Modified</t>
         </is>
       </c>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>08-皮肤名</t>
         </is>
       </c>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>08-Last-Modified</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>09-皮肤名</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>09-Last-Modified</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>10-皮肤名</t>
         </is>
       </c>
-      <c r="X1" s="6" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>10-Last-Modified</t>
         </is>
       </c>
-      <c r="Y1" s="6" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>11-皮肤名</t>
         </is>
       </c>
-      <c r="Z1" s="6" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>11-Last-Modified</t>
         </is>
       </c>
-      <c r="AA1" s="6" t="inlineStr">
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>12-皮肤名</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>12-Last-Modified</t>
         </is>
       </c>
-      <c r="AC1" s="6" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>13-皮肤名</t>
         </is>
       </c>
-      <c r="AD1" s="6" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>13-Last-Modified</t>
         </is>
       </c>
-      <c r="AE1" s="6" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>14-皮肤名</t>
         </is>
       </c>
-      <c r="AF1" s="6" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>14-Last-Modified</t>
         </is>
       </c>
-      <c r="AG1" s="6" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>15-皮肤名</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="AH1" s="7" t="inlineStr">
         <is>
           <t>15-Last-Modified</t>
         </is>
       </c>
-      <c r="AI1" s="6" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>16-皮肤名</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>16-Last-Modified</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>17-皮肤名</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="AL1" s="7" t="inlineStr">
         <is>
           <t>17-Last-Modified</t>
         </is>
       </c>
-      <c r="AM1" s="6" t="inlineStr">
+      <c r="AM1" s="7" t="inlineStr">
         <is>
           <t>18-皮肤名</t>
         </is>
       </c>
-      <c r="AN1" s="6" t="inlineStr">
+      <c r="AN1" s="7" t="inlineStr">
         <is>
           <t>18-Last-Modified</t>
         </is>
       </c>
-      <c r="AO1" s="6" t="inlineStr">
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>19-皮肤名</t>
         </is>
       </c>
-      <c r="AP1" s="6" t="inlineStr">
+      <c r="AP1" s="7" t="inlineStr">
         <is>
           <t>19-Last-Modified</t>
         </is>
@@ -12698,8 +12706,16 @@
           <t>2025-03-12 18:28:09</t>
         </is>
       </c>
-      <c r="Y171" s="1" t="n"/>
-      <c r="Z171" s="1" t="n"/>
+      <c r="Y171" s="6" t="inlineStr">
+        <is>
+          <t>督灵司正</t>
+        </is>
+      </c>
+      <c r="Z171" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04 18:19:08</t>
+        </is>
+      </c>
       <c r="AA171" s="1" t="n"/>
       <c r="AB171" s="1" t="n"/>
       <c r="AC171" s="1" t="n"/>
@@ -15772,8 +15788,16 @@
           <t>2025-08-27 14:24:49</t>
         </is>
       </c>
-      <c r="Y200" s="1" t="n"/>
-      <c r="Z200" s="1" t="n"/>
+      <c r="Y200" s="6" t="inlineStr">
+        <is>
+          <t>碎光执事</t>
+        </is>
+      </c>
+      <c r="Z200" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:14:36</t>
+        </is>
+      </c>
       <c r="AA200" s="1" t="n"/>
       <c r="AB200" s="1" t="n"/>
       <c r="AC200" s="1" t="n"/>
@@ -32096,12 +32120,12 @@
           <t>2023-06-19 16:31:45</t>
         </is>
       </c>
-      <c r="M526" s="5" t="inlineStr">
+      <c r="M526" s="4" t="inlineStr">
         <is>
           <t>傩神司</t>
         </is>
       </c>
-      <c r="N526" s="5" t="inlineStr">
+      <c r="N526" s="4" t="inlineStr">
         <is>
           <t>2026-08-26 15:03:39</t>
         </is>

--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,11 @@
         <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +128,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -37884,8 +37892,12 @@
         <v>630</v>
       </c>
       <c r="B631" s="1" t="n"/>
-      <c r="C631" s="1" t="n"/>
-      <c r="D631" s="1" t="n"/>
+      <c r="C631" s="9" t="n"/>
+      <c r="D631" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:30</t>
+        </is>
+      </c>
       <c r="E631" s="1" t="n"/>
       <c r="F631" s="1" t="n"/>
       <c r="G631" s="1" t="n"/>
@@ -37988,8 +38000,12 @@
         <v>632</v>
       </c>
       <c r="B633" s="1" t="n"/>
-      <c r="C633" s="1" t="n"/>
-      <c r="D633" s="1" t="n"/>
+      <c r="C633" s="9" t="n"/>
+      <c r="D633" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:30</t>
+        </is>
+      </c>
       <c r="E633" s="1" t="n"/>
       <c r="F633" s="1" t="n"/>
       <c r="G633" s="1" t="n"/>
@@ -38034,8 +38050,12 @@
         <v>633</v>
       </c>
       <c r="B634" s="1" t="n"/>
-      <c r="C634" s="1" t="n"/>
-      <c r="D634" s="1" t="n"/>
+      <c r="C634" s="9" t="n"/>
+      <c r="D634" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:31</t>
+        </is>
+      </c>
       <c r="E634" s="1" t="n"/>
       <c r="F634" s="1" t="n"/>
       <c r="G634" s="1" t="n"/>
@@ -38760,8 +38780,12 @@
         <v>648</v>
       </c>
       <c r="B649" s="1" t="n"/>
-      <c r="C649" s="1" t="n"/>
-      <c r="D649" s="1" t="n"/>
+      <c r="C649" s="9" t="n"/>
+      <c r="D649" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:31</t>
+        </is>
+      </c>
       <c r="E649" s="1" t="n"/>
       <c r="F649" s="1" t="n"/>
       <c r="G649" s="1" t="n"/>
@@ -38806,8 +38830,12 @@
         <v>649</v>
       </c>
       <c r="B650" s="1" t="n"/>
-      <c r="C650" s="1" t="n"/>
-      <c r="D650" s="1" t="n"/>
+      <c r="C650" s="9" t="n"/>
+      <c r="D650" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:31</t>
+        </is>
+      </c>
       <c r="E650" s="1" t="n"/>
       <c r="F650" s="1" t="n"/>
       <c r="G650" s="1" t="n"/>
@@ -38944,8 +38972,12 @@
         <v>652</v>
       </c>
       <c r="B653" s="1" t="n"/>
-      <c r="C653" s="1" t="n"/>
-      <c r="D653" s="1" t="n"/>
+      <c r="C653" s="9" t="n"/>
+      <c r="D653" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:43:32</t>
+        </is>
+      </c>
       <c r="E653" s="1" t="n"/>
       <c r="F653" s="1" t="n"/>
       <c r="G653" s="1" t="n"/>

--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -73,6 +73,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
@@ -84,11 +89,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,16 +121,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,212 +546,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>英雄编号</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>英雄名字</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>00-皮肤名</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>00-Last-Modified</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>01-皮肤名</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>01-Last-Modified</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>02-皮肤名</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>02-Last-Modified</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>03-皮肤名</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>03-Last-Modified</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>04-皮肤名</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>04-Last-Modified</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>05-皮肤名</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>05-Last-Modified</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>06-皮肤名</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>06-Last-Modified</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>07-皮肤名</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>07-Last-Modified</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>08-皮肤名</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>08-Last-Modified</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>09-皮肤名</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>09-Last-Modified</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>10-皮肤名</t>
         </is>
       </c>
-      <c r="X1" s="8" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>10-Last-Modified</t>
         </is>
       </c>
-      <c r="Y1" s="8" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>11-皮肤名</t>
         </is>
       </c>
-      <c r="Z1" s="8" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>11-Last-Modified</t>
         </is>
       </c>
-      <c r="AA1" s="8" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>12-皮肤名</t>
         </is>
       </c>
-      <c r="AB1" s="8" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>12-Last-Modified</t>
         </is>
       </c>
-      <c r="AC1" s="8" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>13-皮肤名</t>
         </is>
       </c>
-      <c r="AD1" s="8" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>13-Last-Modified</t>
         </is>
       </c>
-      <c r="AE1" s="8" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>14-皮肤名</t>
         </is>
       </c>
-      <c r="AF1" s="8" t="inlineStr">
+      <c r="AF1" s="9" t="inlineStr">
         <is>
           <t>14-Last-Modified</t>
         </is>
       </c>
-      <c r="AG1" s="8" t="inlineStr">
+      <c r="AG1" s="9" t="inlineStr">
         <is>
           <t>15-皮肤名</t>
         </is>
       </c>
-      <c r="AH1" s="8" t="inlineStr">
+      <c r="AH1" s="9" t="inlineStr">
         <is>
           <t>15-Last-Modified</t>
         </is>
       </c>
-      <c r="AI1" s="8" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>16-皮肤名</t>
         </is>
       </c>
-      <c r="AJ1" s="8" t="inlineStr">
+      <c r="AJ1" s="9" t="inlineStr">
         <is>
           <t>16-Last-Modified</t>
         </is>
       </c>
-      <c r="AK1" s="8" t="inlineStr">
+      <c r="AK1" s="9" t="inlineStr">
         <is>
           <t>17-皮肤名</t>
         </is>
       </c>
-      <c r="AL1" s="8" t="inlineStr">
+      <c r="AL1" s="9" t="inlineStr">
         <is>
           <t>17-Last-Modified</t>
         </is>
       </c>
-      <c r="AM1" s="8" t="inlineStr">
+      <c r="AM1" s="9" t="inlineStr">
         <is>
           <t>18-皮肤名</t>
         </is>
       </c>
-      <c r="AN1" s="8" t="inlineStr">
+      <c r="AN1" s="9" t="inlineStr">
         <is>
           <t>18-Last-Modified</t>
         </is>
       </c>
-      <c r="AO1" s="8" t="inlineStr">
+      <c r="AO1" s="9" t="inlineStr">
         <is>
           <t>19-皮肤名</t>
         </is>
       </c>
-      <c r="AP1" s="8" t="inlineStr">
+      <c r="AP1" s="9" t="inlineStr">
         <is>
           <t>19-Last-Modified</t>
         </is>
@@ -12722,12 +12722,12 @@
           <t>2025-03-12 18:28:09</t>
         </is>
       </c>
-      <c r="Y171" s="7" t="inlineStr">
+      <c r="Y171" s="6" t="inlineStr">
         <is>
           <t>督灵司正</t>
         </is>
       </c>
-      <c r="Z171" s="7" t="inlineStr">
+      <c r="Z171" s="6" t="inlineStr">
         <is>
           <t>2026-09-08 12:09:44</t>
         </is>
@@ -30050,12 +30050,12 @@
       </c>
       <c r="M504" s="1" t="n"/>
       <c r="N504" s="1" t="n"/>
-      <c r="O504" s="7" t="inlineStr">
+      <c r="O504" s="6" t="inlineStr">
         <is>
           <t>铁影缉凶</t>
         </is>
       </c>
-      <c r="P504" s="7" t="inlineStr">
+      <c r="P504" s="6" t="inlineStr">
         <is>
           <t>2026-09-08 17:42:30</t>
         </is>
@@ -37887,13 +37887,21 @@
       <c r="AO630" s="1" t="n"/>
       <c r="AP630" s="1" t="n"/>
     </row>
-    <row r="631" hidden="1">
+    <row r="631">
       <c r="A631" s="1" t="n">
         <v>630</v>
       </c>
-      <c r="B631" s="1" t="n"/>
-      <c r="C631" s="9" t="n"/>
-      <c r="D631" s="9" t="inlineStr">
+      <c r="B631" s="1" t="inlineStr">
+        <is>
+          <t>莉莉安</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D631" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:30</t>
         </is>
@@ -37995,13 +38003,21 @@
       <c r="AO632" s="1" t="n"/>
       <c r="AP632" s="1" t="n"/>
     </row>
-    <row r="633" hidden="1">
+    <row r="633">
       <c r="A633" s="1" t="n">
         <v>632</v>
       </c>
-      <c r="B633" s="1" t="n"/>
-      <c r="C633" s="9" t="n"/>
-      <c r="D633" s="9" t="inlineStr">
+      <c r="B633" s="1" t="inlineStr">
+        <is>
+          <t>绯泪</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D633" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:30</t>
         </is>
@@ -38045,13 +38061,21 @@
       <c r="AO633" s="1" t="n"/>
       <c r="AP633" s="1" t="n"/>
     </row>
-    <row r="634" hidden="1">
+    <row r="634">
       <c r="A634" s="1" t="n">
         <v>633</v>
       </c>
-      <c r="B634" s="1" t="n"/>
-      <c r="C634" s="9" t="n"/>
-      <c r="D634" s="9" t="inlineStr">
+      <c r="B634" s="1" t="inlineStr">
+        <is>
+          <t>卡芬妮</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D634" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:31</t>
         </is>
@@ -38775,13 +38799,21 @@
       <c r="AO648" s="1" t="n"/>
       <c r="AP648" s="1" t="n"/>
     </row>
-    <row r="649" hidden="1">
+    <row r="649">
       <c r="A649" s="1" t="n">
         <v>648</v>
       </c>
-      <c r="B649" s="1" t="n"/>
-      <c r="C649" s="9" t="n"/>
-      <c r="D649" s="9" t="inlineStr">
+      <c r="B649" s="1" t="inlineStr">
+        <is>
+          <t>星葵</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D649" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:31</t>
         </is>
@@ -38825,13 +38857,21 @@
       <c r="AO649" s="1" t="n"/>
       <c r="AP649" s="1" t="n"/>
     </row>
-    <row r="650" hidden="1">
+    <row r="650">
       <c r="A650" s="1" t="n">
         <v>649</v>
       </c>
-      <c r="B650" s="1" t="n"/>
-      <c r="C650" s="9" t="n"/>
-      <c r="D650" s="9" t="inlineStr">
+      <c r="B650" s="1" t="inlineStr">
+        <is>
+          <t>皮皮</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D650" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:31</t>
         </is>
@@ -38967,13 +39007,21 @@
       <c r="AO652" s="1" t="n"/>
       <c r="AP652" s="1" t="n"/>
     </row>
-    <row r="653" hidden="1">
+    <row r="653">
       <c r="A653" s="1" t="n">
         <v>652</v>
       </c>
-      <c r="B653" s="1" t="n"/>
-      <c r="C653" s="9" t="n"/>
-      <c r="D653" s="9" t="inlineStr">
+      <c r="B653" s="1" t="inlineStr">
+        <is>
+          <t>索文</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>原皮</t>
+        </is>
+      </c>
+      <c r="D653" s="8" t="inlineStr">
         <is>
           <t>2026-09-09 14:43:32</t>
         </is>

--- a/hero_skin_scan.xlsx
+++ b/hero_skin_scan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FeverApps\123\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA640EB-0C02-48CC-9582-C9FE42E70E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC6DB02-56AF-4D3D-989D-43AA12141C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="1539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="1544">
   <si>
     <t>英雄编号</t>
   </si>
@@ -1738,6 +1738,9 @@
     <t>2026-02-11 18:07:49</t>
   </si>
   <si>
+    <t>2026-09-21 14:39:28</t>
+  </si>
+  <si>
     <t>程咬金</t>
   </si>
   <si>
@@ -3295,6 +3298,9 @@
     <t>2021-09-23 00:02:38</t>
   </si>
   <si>
+    <t>浑沌棋</t>
+  </si>
+  <si>
     <t>2021-09-23 00:02:46</t>
   </si>
   <si>
@@ -3700,6 +3706,9 @@
     <t>2026-02-11 16:46:28</t>
   </si>
   <si>
+    <t>2026-09-22 17:11:04</t>
+  </si>
+  <si>
     <t>盾山</t>
   </si>
   <si>
@@ -4639,7 +4648,15 @@
     <t>2026-09-09 14:43:32</t>
   </si>
   <si>
-    <t>浑沌棋</t>
+    <t>旅行日记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月影弦鸣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星光竞辉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4669,7 +4686,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4685,6 +4702,11 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -4725,7 +4747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4748,7 +4770,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13140,8 +13168,12 @@
       <c r="AD143" s="1"/>
       <c r="AE143" s="1"/>
       <c r="AF143" s="1"/>
-      <c r="AG143" s="1"/>
-      <c r="AH143" s="1"/>
+      <c r="AG143" s="9" t="s">
+        <v>1541</v>
+      </c>
+      <c r="AH143" s="10">
+        <v>46286.61074074074</v>
+      </c>
       <c r="AI143" s="1"/>
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
@@ -13202,7 +13234,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>43</v>
@@ -13211,7 +13243,7 @@
         <v>542</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>166</v>
@@ -13223,46 +13255,46 @@
         <v>354</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>435</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>452</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P145" s="2" t="s">
         <v>100</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S145" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="T145" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="U145" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="V145" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
@@ -13336,63 +13368,63 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>540</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L147" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P147" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="R147" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="S147" s="1"/>
       <c r="T147" s="1"/>
       <c r="U147" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="V147" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
@@ -13466,51 +13498,51 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G149" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="H149" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="I149" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
       <c r="O149" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P149" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="R149" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="S149" s="1"/>
       <c r="T149" s="1"/>
@@ -13542,45 +13574,45 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
       <c r="I150" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>122</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
@@ -13614,69 +13646,69 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>166</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>540</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P151" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Q151" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="T151" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="X151" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
@@ -13702,27 +13734,27 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
       <c r="I152" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J152" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
@@ -13762,79 +13794,79 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1"/>
       <c r="O153" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P153" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="T153" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="U153" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="V153" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="W153" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="X153" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
       <c r="AC153" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AD153" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AE153" s="1"/>
       <c r="AF153" s="1"/>
@@ -13854,7 +13886,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>43</v>
@@ -13863,58 +13895,58 @@
         <v>152</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I154" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="J154" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="J154" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="K154" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P154" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T154" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U154" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="V154" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
@@ -13942,73 +13974,73 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L155" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>540</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Q155" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R155" s="2" t="s">
         <v>452</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="T155" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="U155" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="V155" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="W155" s="2" t="s">
         <v>157</v>
       </c>
       <c r="X155" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
@@ -14034,55 +14066,55 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="P156" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="S156" s="1"/>
       <c r="T156" s="1"/>
@@ -14114,67 +14146,67 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>540</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="P157" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="R157" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="T157" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U157" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="V157" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
@@ -14202,7 +14234,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>43</v>
@@ -14211,22 +14243,22 @@
         <v>354</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>500</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
@@ -14312,43 +14344,43 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
@@ -14476,25 +14508,25 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -14536,7 +14568,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>43</v>
@@ -14545,16 +14577,16 @@
         <v>76</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -14688,34 +14720,34 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="L167" s="2" t="s">
         <v>116</v>
@@ -14727,33 +14759,37 @@
         <v>563</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="R167" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="T167" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="U167" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="V167" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
-      <c r="Y167" s="1"/>
-      <c r="Z167" s="1"/>
+      <c r="Y167" s="9" t="s">
+        <v>1541</v>
+      </c>
+      <c r="Z167" s="9" t="s">
+        <v>571</v>
+      </c>
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
@@ -14776,73 +14812,73 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M168" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="O168" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="Q168" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R168" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="T168" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="U168" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="V168" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="W168" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="X168" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Y168" s="2" t="s">
         <v>104</v>
@@ -14872,7 +14908,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>43</v>
@@ -14881,46 +14917,46 @@
         <v>146</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>452</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O169" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P169" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="R169" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -14952,85 +14988,85 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>540</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="L170" s="2" t="s">
         <v>540</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O170" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="Q170" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="R170" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="T170" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="U170" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="V170" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="W170" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="X170" s="2" t="s">
         <v>419</v>
       </c>
       <c r="Y170" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="Z170" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AA170" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AB170" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
@@ -15052,7 +15088,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>43</v>
@@ -15061,34 +15097,34 @@
         <v>500</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>535</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K171" s="2" t="s">
         <v>155</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M171" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O171" s="2" t="s">
         <v>338</v>
@@ -15099,24 +15135,24 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="T171" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="X171" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="Y171" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="Z171" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
@@ -15140,7 +15176,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>43</v>
@@ -15149,24 +15185,24 @@
         <v>500</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
       <c r="K172" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="M172" s="2" t="s">
         <v>338</v>
@@ -15175,18 +15211,18 @@
         <v>529</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="T172" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
@@ -15216,19 +15252,19 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G173" s="1"/>
       <c r="H173" s="1"/>
@@ -15272,61 +15308,61 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M174" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="O174" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="Q174" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="R174" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="T174" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="U174" s="2" t="s">
         <v>176</v>
@@ -15337,10 +15373,10 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="Z174" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
@@ -15364,7 +15400,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>43</v>
@@ -15373,34 +15409,34 @@
         <v>100</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>488</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>500</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="L175" s="2" t="s">
         <v>100</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
@@ -15411,28 +15447,28 @@
         <v>491</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="T175" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="U175" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="V175" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="W175" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="X175" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Y175" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="Z175" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
@@ -15456,19 +15492,19 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>104</v>
@@ -15477,28 +15513,28 @@
         <v>100</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="O176" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
@@ -15532,7 +15568,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>43</v>
@@ -15541,13 +15577,13 @@
         <v>540</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>456</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>100</v>
@@ -15555,22 +15591,22 @@
       <c r="I177" s="1"/>
       <c r="J177" s="1"/>
       <c r="K177" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="O177" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="P177" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
@@ -15604,33 +15640,33 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G178" s="1"/>
       <c r="H178" s="1"/>
       <c r="I178" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="J178" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M178" s="1"/>
       <c r="N178" s="1"/>
@@ -15668,40 +15704,40 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G179" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="H179" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="H179" s="2" t="s">
-        <v>894</v>
-      </c>
       <c r="I179" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J179" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="L179" s="2" t="s">
         <v>354</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="N179" s="2" t="s">
         <v>274</v>
@@ -15709,22 +15745,22 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="Q179" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="T179" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="U179" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="V179" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
@@ -15752,43 +15788,43 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
@@ -15824,7 +15860,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>43</v>
@@ -15833,46 +15869,46 @@
         <v>76</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M181" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -15950,61 +15986,61 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="J183" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M183" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="R183" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="S183" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="T183" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
@@ -16034,55 +16070,55 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G184" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="H184" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="H184" s="2" t="s">
-        <v>944</v>
-      </c>
       <c r="I184" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="J184" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="S184" s="1"/>
       <c r="T184" s="1"/>
@@ -16114,77 +16150,77 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>500</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J185" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="L185" s="2" t="s">
         <v>76</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="P185" s="2" t="s">
         <v>209</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="T185" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="X185" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
       <c r="AA185" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AB185" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
@@ -16252,51 +16288,51 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>116</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="J187" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M187" s="1"/>
       <c r="N187" s="1"/>
       <c r="O187" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="P187" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="S187" s="1"/>
       <c r="T187" s="1"/>
@@ -16328,43 +16364,43 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="J188" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M188" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
@@ -16400,19 +16436,19 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
@@ -16456,57 +16492,57 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>456</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M190" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="T190" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
@@ -16536,63 +16572,63 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="J191" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M191" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="O191" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="P191" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q191" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="R191" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="S191" s="1"/>
       <c r="T191" s="1"/>
       <c r="U191" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="V191" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
@@ -16620,7 +16656,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>43</v>
@@ -16629,46 +16665,46 @@
         <v>122</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J192" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M192" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="N192" s="2" t="s">
         <v>535</v>
       </c>
       <c r="O192" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="Q192" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="S192" s="2" t="s">
         <v>127</v>
@@ -16677,16 +16713,16 @@
         <v>175</v>
       </c>
       <c r="U192" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="V192" s="2" t="s">
         <v>162</v>
       </c>
       <c r="W192" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="X192" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
@@ -16712,41 +16748,41 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
       <c r="I193" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J193" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M193" s="1"/>
       <c r="N193" s="1"/>
       <c r="O193" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="P193" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
@@ -16754,7 +16790,7 @@
         <v>338</v>
       </c>
       <c r="T193" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
@@ -16784,67 +16820,67 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J194" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="L194" s="2" t="s">
         <v>205</v>
       </c>
       <c r="M194" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="Q194" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="T194" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="U194" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="V194" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
@@ -16872,7 +16908,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>43</v>
@@ -16881,40 +16917,40 @@
         <v>219</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>74</v>
       </c>
       <c r="O195" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="P195" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
@@ -16948,49 +16984,49 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J196" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="L196" s="2" t="s">
         <v>219</v>
       </c>
       <c r="M196" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="O196" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
@@ -17024,16 +17060,16 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>100</v>
@@ -17041,28 +17077,28 @@
       <c r="G197" s="1"/>
       <c r="H197" s="1"/>
       <c r="I197" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="J197" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="M197" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="O197" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="P197" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="Q197" s="2" t="s">
         <v>338</v>
@@ -17073,13 +17109,13 @@
       <c r="S197" s="1"/>
       <c r="T197" s="1"/>
       <c r="U197" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="V197" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="W197" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="X197" s="2" t="s">
         <v>276</v>
@@ -17108,49 +17144,49 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>1538</v>
+        <v>1091</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="J198" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="M198" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="O198" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
@@ -17184,43 +17220,43 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="J199" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
@@ -17256,75 +17292,75 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>354</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="J200" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="M200" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="O200" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="S200" s="1"/>
       <c r="T200" s="1"/>
       <c r="U200" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="V200" s="2" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="W200" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="X200" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Y200" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Z200" s="5" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
@@ -22500,61 +22536,61 @@
         <v>312</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="J313" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="K313" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="L313" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="M313" s="2" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="N313" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="O313" s="2" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="P313" s="2" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="Q313" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="R313" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="S313" s="2" t="s">
         <v>210</v>
       </c>
       <c r="T313" s="2" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
@@ -31232,7 +31268,7 @@
         <v>501</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>43</v>
@@ -31241,52 +31277,52 @@
         <v>354</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="F502" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="K502" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L502" s="2" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="M502" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="N502" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="O502" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="P502" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="Q502" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="R502" s="2" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="T502" s="2" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="U502" s="1"/>
       <c r="V502" s="1"/>
@@ -31316,57 +31352,57 @@
         <v>502</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="F503" s="2" t="s">
         <v>124</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="I503" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="K503" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="L503" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="M503" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="N503" s="2" t="s">
         <v>50</v>
       </c>
       <c r="O503" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="P503" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="Q503" s="1"/>
       <c r="R503" s="1"/>
       <c r="S503" s="2" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="T503" s="2" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="U503" s="1"/>
       <c r="V503" s="1"/>
@@ -31396,51 +31432,51 @@
         <v>503</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="K504" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="L504" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="M504" s="1"/>
       <c r="N504" s="1"/>
       <c r="O504" s="6" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="P504" s="6" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="Q504" s="2" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="R504" s="2" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="S504" s="1"/>
       <c r="T504" s="1"/>
@@ -31472,55 +31508,55 @@
         <v>504</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F505" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="H505" s="2" t="s">
         <v>124</v>
       </c>
       <c r="I505" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="K505" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="L505" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="M505" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="N505" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="O505" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="P505" s="2" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="Q505" s="2" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="R505" s="2" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="S505" s="1"/>
       <c r="T505" s="1"/>
@@ -31552,52 +31588,52 @@
         <v>505</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="I506" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="K506" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="L506" s="2" t="s">
         <v>68</v>
       </c>
       <c r="M506" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N506" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="O506" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="P506" s="2" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="Q506" s="2" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="R506" s="2" t="s">
         <v>566</v>
@@ -31632,43 +31668,43 @@
         <v>506</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="F507" s="2" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="I507" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="K507" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L507" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M507" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="N507" s="2" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="O507" s="1"/>
       <c r="P507" s="1"/>
@@ -31704,37 +31740,37 @@
         <v>507</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F508" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G508" s="2" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="H508" s="2" t="s">
         <v>452</v>
       </c>
       <c r="I508" s="2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J508" s="2" t="s">
         <v>68</v>
       </c>
       <c r="K508" s="2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="L508" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="M508" s="1"/>
       <c r="N508" s="1"/>
@@ -31772,68 +31808,72 @@
         <v>508</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="F509" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G509" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="I509" s="2" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="J509" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="K509" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="L509" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M509" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="N509" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="O509" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="P509" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="Q509" s="1"/>
       <c r="R509" s="1"/>
       <c r="S509" s="2" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="T509" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="U509" s="2" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="V509" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="W509" s="1"/>
       <c r="X509" s="1"/>
-      <c r="Y509" s="1"/>
-      <c r="Z509" s="1"/>
+      <c r="Y509" s="9" t="s">
+        <v>1542</v>
+      </c>
+      <c r="Z509" s="9" t="s">
+        <v>1227</v>
+      </c>
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
       <c r="AC509" s="1"/>
@@ -31856,37 +31896,37 @@
         <v>509</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="F510" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G510" s="2" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="I510" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J510" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K510" s="2" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="L510" s="2" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="M510" s="1"/>
       <c r="N510" s="1"/>
@@ -31924,7 +31964,7 @@
         <v>510</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>43</v>
@@ -31933,37 +31973,37 @@
         <v>452</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="F511" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="G511" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="I511" s="2" t="s">
         <v>153</v>
       </c>
       <c r="J511" s="2" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="K511" s="2" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="L511" s="2" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="M511" s="2" t="s">
         <v>127</v>
       </c>
       <c r="N511" s="2" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="O511" s="2" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="P511" s="2" t="s">
         <v>162</v>
@@ -32004,34 +32044,34 @@
         <v>511</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="F512" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="K512" s="2" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="L512" s="2" t="s">
         <v>550</v>
@@ -32039,10 +32079,10 @@
       <c r="M512" s="1"/>
       <c r="N512" s="1"/>
       <c r="O512" s="2" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="P512" s="2" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="Q512" s="1"/>
       <c r="R512" s="1"/>
@@ -32122,57 +32162,57 @@
         <v>513</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="F514" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="K514" s="2" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="L514" s="2" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="M514" s="2" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="N514" s="2" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="O514" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P514" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q514" s="1"/>
       <c r="R514" s="1"/>
       <c r="S514" s="2" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="T514" s="2" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="U514" s="1"/>
       <c r="V514" s="1"/>
@@ -32202,37 +32242,37 @@
         <v>514</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F515" s="2" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="I515" s="2" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="K515" s="2" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="L515" s="2" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="M515" s="1"/>
       <c r="N515" s="1"/>
@@ -32270,49 +32310,49 @@
         <v>515</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="F516" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="I516" s="2" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="J516" s="2" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="K516" s="2" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="L516" s="2" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="M516" s="2" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="N516" s="2" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="O516" s="2" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="P516" s="2" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="Q516" s="1"/>
       <c r="R516" s="1"/>
@@ -32392,37 +32432,37 @@
         <v>517</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="F518" s="2" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="G518" s="2" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="I518" s="2" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="J518" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="K518" s="2" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="L518" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="M518" s="1"/>
       <c r="N518" s="1"/>
@@ -32460,7 +32500,7 @@
         <v>518</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>43</v>
@@ -32469,42 +32509,42 @@
         <v>500</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="F519" s="2" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="G519" s="1"/>
       <c r="H519" s="1"/>
       <c r="I519" s="2" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="J519" s="2" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="K519" s="2" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="L519" s="2" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="M519" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="N519" s="2" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="O519" s="2" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="P519" s="2" t="s">
         <v>265</v>
       </c>
       <c r="Q519" s="2" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="R519" s="2" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="S519" s="1"/>
       <c r="T519" s="1"/>
@@ -32536,25 +32576,25 @@
         <v>519</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="F520" s="2" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="G520" s="2" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -32642,50 +32682,50 @@
         <v>521</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="F522" s="2" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="K522" s="2" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="L522" s="2" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="M522" s="1"/>
       <c r="N522" s="1"/>
       <c r="O522" s="2" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="P522" s="2" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="Q522" s="1"/>
       <c r="R522" s="1"/>
       <c r="S522" s="2" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="T522" s="2" t="s">
         <v>276</v>
@@ -32718,13 +32758,13 @@
         <v>522</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>258</v>
@@ -32733,28 +32773,28 @@
         <v>452</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="K523" s="2" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="L523" s="2" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="M523" s="2" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="N523" s="2" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="O523" s="1"/>
       <c r="P523" s="1"/>
@@ -32790,13 +32830,13 @@
         <v>523</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>258</v>
@@ -32807,46 +32847,46 @@
       <c r="G524" s="1"/>
       <c r="H524" s="1"/>
       <c r="I524" s="2" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="K524" s="2" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="L524" s="2" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="M524" s="2" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="N524" s="2" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="O524" s="2" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="P524" s="2" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="Q524" s="2" t="s">
         <v>373</v>
       </c>
       <c r="R524" s="2" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="T524" s="2" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="U524" s="2" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="V524" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="W524" s="1"/>
       <c r="X524" s="1"/>
@@ -32874,7 +32914,7 @@
         <v>524</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>43</v>
@@ -32886,37 +32926,37 @@
         <v>258</v>
       </c>
       <c r="F525" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="H525" s="2" t="s">
         <v>500</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K525" s="2" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="L525" s="2" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="M525" s="2" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="N525" s="2" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="O525" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="P525" s="2" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="Q525" s="1"/>
       <c r="R525" s="1"/>
@@ -32950,43 +32990,43 @@
         <v>525</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>258</v>
       </c>
       <c r="F526" s="2" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="H526" s="2" t="s">
         <v>354</v>
       </c>
       <c r="I526" s="2" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="K526" s="2" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="L526" s="2" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="M526" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N526" s="4" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="O526" s="1"/>
       <c r="P526" s="1"/>
@@ -33068,37 +33108,37 @@
         <v>527</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G528" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="I528" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="J528" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K528" s="2" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="L528" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="M528" s="1"/>
       <c r="N528" s="1"/>
@@ -33136,51 +33176,51 @@
         <v>528</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="G529" s="2" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="I529" s="2" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="J529" s="2" t="s">
         <v>209</v>
       </c>
       <c r="K529" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="L529" s="2" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="M529" s="1"/>
       <c r="N529" s="1"/>
       <c r="O529" s="2" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="P529" s="2" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="Q529" s="2" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="R529" s="2" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="S529" s="1"/>
       <c r="T529" s="1"/>
@@ -33212,51 +33252,51 @@
         <v>529</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D530" s="2" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F530" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="I530" s="2" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="J530" s="2" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="K530" s="2" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="L530" s="2" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="M530" s="2" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="N530" s="2" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="O530" s="1"/>
       <c r="P530" s="1"/>
       <c r="Q530" s="2" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="R530" s="2" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="S530" s="1"/>
       <c r="T530" s="1"/>
@@ -33288,25 +33328,25 @@
         <v>530</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>407</v>
       </c>
       <c r="F531" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="G531" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="I531" s="1"/>
       <c r="J531" s="1"/>
@@ -33314,25 +33354,25 @@
         <v>410</v>
       </c>
       <c r="L531" s="2" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="M531" s="2" t="s">
         <v>412</v>
       </c>
       <c r="N531" s="2" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="O531" s="2" t="s">
         <v>414</v>
       </c>
       <c r="P531" s="2" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="Q531" s="2" t="s">
         <v>416</v>
       </c>
       <c r="R531" s="2" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="S531" s="1"/>
       <c r="T531" s="1"/>
@@ -33364,49 +33404,49 @@
         <v>531</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="F532" s="2" t="s">
         <v>452</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="K532" s="2" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="L532" s="2" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="M532" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N532" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="O532" s="2" t="s">
         <v>492</v>
       </c>
       <c r="P532" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="Q532" s="1"/>
       <c r="R532" s="1"/>
@@ -33486,37 +33526,37 @@
         <v>533</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="F534" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="H534" s="2" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="I534" s="2" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="K534" s="2" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="L534" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M534" s="1"/>
       <c r="N534" s="1"/>
@@ -33554,49 +33594,49 @@
         <v>534</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="F535" s="2" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="K535" s="2" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="L535" s="2" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="M535" s="2" t="s">
         <v>71</v>
       </c>
       <c r="N535" s="2" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="O535" s="2" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="P535" s="2" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="Q535" s="1"/>
       <c r="R535" s="1"/>
@@ -33676,25 +33716,25 @@
         <v>536</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="F537" s="2" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -33736,31 +33776,31 @@
         <v>537</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="F538" s="2" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="G538" s="2" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H538" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="I538" s="2" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="J538" s="2" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="K538" s="1"/>
       <c r="L538" s="1"/>
@@ -33800,43 +33840,43 @@
         <v>538</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="F539" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G539" s="2" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="H539" s="2" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="I539" s="2" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="J539" s="2" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="K539" s="2" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="L539" s="2" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="M539" s="2" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="N539" s="2" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="O539" s="1"/>
       <c r="P539" s="1"/>
@@ -33918,31 +33958,31 @@
         <v>540</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="F541" s="2" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="G541" s="2" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="J541" s="2" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="K541" s="1"/>
       <c r="L541" s="1"/>
@@ -34028,39 +34068,39 @@
         <v>542</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="F543" s="2" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
       <c r="G543" s="2" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="I543" s="2" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
       <c r="J543" s="2" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="K543" s="1"/>
       <c r="L543" s="1"/>
       <c r="M543" s="2" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="N543" s="2" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="O543" s="1"/>
       <c r="P543" s="1"/>
@@ -34142,39 +34182,39 @@
         <v>544</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="G545" s="2" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="I545" s="2" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="J545" s="2" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="K545" s="1"/>
       <c r="L545" s="1"/>
       <c r="M545" s="2" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="N545" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O545" s="1"/>
       <c r="P545" s="1"/>
@@ -34210,41 +34250,41 @@
         <v>545</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="F546" s="2" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="G546" s="2" t="s">
         <v>153</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
       <c r="K546" s="2" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="L546" s="2" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="M546" s="1"/>
       <c r="N546" s="1"/>
       <c r="O546" s="2" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="P546" s="2" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="Q546" s="1"/>
       <c r="R546" s="1"/>
@@ -34324,13 +34364,13 @@
         <v>547</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="E548" s="1"/>
       <c r="F548" s="1"/>
@@ -34376,28 +34416,28 @@
         <v>548</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="F549" s="2" t="s">
         <v>528</v>
       </c>
       <c r="G549" s="2" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="I549" s="2" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="J549" s="2" t="s">
         <v>305</v>
@@ -34440,19 +34480,19 @@
         <v>549</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="G550" s="1"/>
       <c r="H550" s="1"/>
@@ -34496,16 +34536,16 @@
         <v>550</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="F551" s="2" t="s">
         <v>251</v>
@@ -34874,25 +34914,25 @@
         <v>558</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="F559" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G559" s="2" t="s">
         <v>338</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="I559" s="1"/>
       <c r="J559" s="1"/>
@@ -35118,38 +35158,42 @@
         <v>563</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="F564" s="2" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="G564" s="2" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="H564" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
       <c r="K564" s="2" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="L564" s="2" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="M564" s="1"/>
       <c r="N564" s="1"/>
-      <c r="O564" s="1"/>
-      <c r="P564" s="1"/>
+      <c r="O564" s="9" t="s">
+        <v>1543</v>
+      </c>
+      <c r="P564" s="10">
+        <v>46286.629108796296</v>
+      </c>
       <c r="Q564" s="1"/>
       <c r="R564" s="1"/>
       <c r="S564" s="1"/>
@@ -35182,53 +35226,53 @@
         <v>564</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="F565" s="2" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="G565" s="2" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
       <c r="K565" s="2" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="L565" s="2" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="M565" s="2" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="N565" s="2" t="s">
         <v>143</v>
       </c>
       <c r="O565" s="2" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="P565" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Q565" s="1"/>
       <c r="R565" s="1"/>
       <c r="S565" s="2" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="T565" s="2" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="U565" s="1"/>
       <c r="V565" s="1"/>
@@ -35810,33 +35854,33 @@
         <v>577</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="F578" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G578" s="2" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
       <c r="K578" s="2" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="L578" s="2" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="M578" s="1"/>
       <c r="N578" s="1"/>
@@ -38266,13 +38310,13 @@
         <v>630</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D631" s="7" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="E631" s="1"/>
       <c r="F631" s="1"/>
@@ -38318,13 +38362,13 @@
         <v>631</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="C632" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="E632" s="1"/>
       <c r="F632" s="1"/>
@@ -38370,13 +38414,13 @@
         <v>632</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D633" s="7" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="E633" s="1"/>
       <c r="F633" s="1"/>
@@ -38422,13 +38466,13 @@
         <v>633</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D634" s="7" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="E634" s="1"/>
       <c r="F634" s="1"/>
@@ -38520,13 +38564,13 @@
         <v>635</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="C636" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="E636" s="1"/>
       <c r="F636" s="1"/>
@@ -38756,13 +38800,13 @@
         <v>640</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="E641" s="1"/>
       <c r="F641" s="1"/>
@@ -39038,13 +39082,13 @@
         <v>646</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="E647" s="1"/>
       <c r="F647" s="1"/>
@@ -39136,13 +39180,13 @@
         <v>648</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D649" s="7" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="E649" s="1"/>
       <c r="F649" s="1"/>
@@ -39188,13 +39232,13 @@
         <v>649</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D650" s="7" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="E650" s="1"/>
       <c r="F650" s="1"/>
@@ -39332,13 +39376,13 @@
         <v>652</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="C653" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D653" s="7" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="E653" s="1"/>
       <c r="F653" s="1"/>
